--- a/Sistematización fuentes originales - Proyecto Provincias - v4.xlsx
+++ b/Sistematización fuentes originales - Proyecto Provincias - v4.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fuentes'!$A$1:$X$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fuentes'!$A$1:$AB$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Variables'!$A$1:$P$336</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Excluidos'!$A$1:$M$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Brechas'!$A$1:$H$16</definedName>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X177"/>
+  <dimension ref="A1:AB177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,10 @@
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,6 +604,26 @@
           <t>estado_migracion</t>
         </is>
       </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>nivel_procedencia</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>evidencia_procedencia</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>fecha_consulta</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>condiciones_uso</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -698,6 +722,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -791,6 +820,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -874,6 +908,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -962,6 +1001,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1050,6 +1094,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1138,6 +1187,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1236,6 +1290,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1339,6 +1398,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1437,6 +1501,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1525,6 +1594,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1618,6 +1692,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1716,6 +1795,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1814,6 +1898,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1912,6 +2001,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2000,6 +2094,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2088,6 +2187,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2181,6 +2285,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2284,6 +2393,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2387,6 +2501,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2475,6 +2594,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2568,6 +2692,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2666,6 +2795,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2754,6 +2888,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2842,6 +2981,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2930,6 +3074,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3018,6 +3167,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3116,6 +3270,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3214,6 +3373,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3302,6 +3466,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3405,6 +3574,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3503,6 +3677,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3588,6 +3767,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3673,6 +3857,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3776,6 +3965,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3869,6 +4063,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3972,6 +4171,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4065,6 +4269,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4153,6 +4362,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4251,6 +4465,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4346,6 +4565,11 @@
           <t>No copiado: pesado, pendiente decisión ejecutiva</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4434,6 +4658,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4522,6 +4751,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4610,6 +4844,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4703,6 +4942,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4796,6 +5040,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4881,6 +5130,11 @@
           <t>No copiado: pesado, pendiente decisión ejecutiva</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4984,6 +5238,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5077,6 +5336,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5180,6 +5444,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5278,6 +5547,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5371,6 +5645,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5469,6 +5748,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5567,6 +5851,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5660,6 +5949,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5753,6 +6047,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5846,6 +6145,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5944,6 +6248,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6037,6 +6346,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6125,6 +6439,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6213,6 +6532,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6311,6 +6635,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6404,6 +6733,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6507,6 +6841,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6615,6 +6954,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6700,6 +7044,11 @@
           <t>No copiado: pesado, pendiente decisión ejecutiva</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6785,6 +7134,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6870,6 +7224,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6955,6 +7314,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7040,6 +7404,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7125,6 +7494,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7210,6 +7584,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7295,6 +7674,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7380,6 +7764,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7465,6 +7854,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7550,6 +7944,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7635,6 +8034,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7720,6 +8124,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7805,6 +8214,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7890,6 +8304,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7975,6 +8394,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8060,6 +8484,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8145,6 +8574,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8230,6 +8664,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8315,6 +8754,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8400,6 +8844,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8485,6 +8934,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8570,6 +9024,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8655,6 +9114,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8740,6 +9204,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8825,6 +9294,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8910,6 +9384,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8995,6 +9474,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9080,6 +9564,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9165,6 +9654,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9250,6 +9744,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9335,6 +9834,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9420,6 +9924,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9505,6 +10014,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9590,6 +10104,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9675,6 +10194,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9760,6 +10284,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9845,6 +10374,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9930,6 +10464,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10015,6 +10554,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10100,6 +10644,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10185,6 +10734,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10270,6 +10824,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10355,6 +10914,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10440,6 +11004,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10525,6 +11094,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10610,6 +11184,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10695,6 +11274,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10780,6 +11364,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10865,6 +11454,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10950,6 +11544,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11035,6 +11634,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11120,6 +11724,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11205,6 +11814,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11290,6 +11904,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11375,6 +11994,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11460,6 +12084,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11545,6 +12174,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11630,6 +12264,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11715,6 +12354,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11800,6 +12444,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11885,6 +12534,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11970,6 +12624,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12055,6 +12714,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12140,6 +12804,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12225,6 +12894,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12310,6 +12984,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12395,6 +13074,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12480,6 +13164,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12565,6 +13254,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12650,6 +13344,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12735,6 +13434,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12820,6 +13524,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12905,6 +13614,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12990,6 +13704,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13075,6 +13794,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13160,6 +13884,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13245,6 +13974,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13330,6 +14064,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13415,6 +14154,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13500,6 +14244,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13585,6 +14334,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13670,6 +14424,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13755,6 +14514,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13840,6 +14604,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13925,6 +14694,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14010,6 +14784,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14095,6 +14874,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14180,6 +14964,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14265,6 +15054,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14350,6 +15144,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14435,6 +15234,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14538,6 +15342,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14636,6 +15445,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14739,6 +15553,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14837,6 +15656,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14935,6 +15759,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15023,6 +15852,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15126,6 +15960,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15224,6 +16063,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15322,6 +16166,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15425,6 +16274,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15515,6 +16369,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15600,6 +16459,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15685,6 +16549,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15768,6 +16637,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15848,6 +16722,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15928,6 +16807,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16008,6 +16892,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16101,6 +16990,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16189,6 +17083,11 @@
           <t>Copiado (MD5 verificado)</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16264,9 +17163,14 @@
           <t>Por construir</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Por construir</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X177"/>
+  <autoFilter ref="A1:AB177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -77161,7 +78065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -77475,6 +78379,23 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuentes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nivel_procedencia / evidencia_procedencia / fecha_consulta / condiciones_uso</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Resultado del protocolo de investigación de procedencia (anexo, sección 13). Niveles: Verificada · Documentada · Por confirmar · Desconocida. Toda URL registrada lleva su fecha de consulta.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
